--- a/output/pdf_financials_xlsx/CEF.xlsx
+++ b/output/pdf_financials_xlsx/CEF.xlsx
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.179724</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.252702</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.679</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.404</v>
       </c>
     </row>
     <row r="35">
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.179724</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.252702</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.679</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.404</v>
       </c>
     </row>
     <row r="37">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEF.xlsx
+++ b/output/pdf_financials_xlsx/CEF.xlsx
@@ -3450,22 +3450,16 @@
         <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>7.231813</v>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-05</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.179724</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.679</v>
       </c>
     </row>
     <row r="131">
@@ -3500,7 +3494,7 @@
         <v>1e-05</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>-7.052089</v>
+        <v>0.179714</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>1.072978</v>
@@ -3524,20 +3518,14 @@
       <c r="C133" s="3" t="n">
         <v>0.179724</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>1.252702</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>3.404</v>
       </c>
     </row>
     <row r="134">
@@ -5130,7 +5118,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -5165,7 +5157,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
